--- a/datasets/day1_excel_foundations/06_sorting_filtering_organizing/d1_m6_sorting_start.xlsx
+++ b/datasets/day1_excel_foundations/06_sorting_filtering_organizing/d1_m6_sorting_start.xlsx
@@ -574,7 +574,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>119.7</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
@@ -610,7 +610,7 @@
         <v>2</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3332</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="5">
@@ -646,7 +646,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1454.4</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="6">
@@ -682,7 +682,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>806</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7">
@@ -718,7 +718,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1656</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="8">
@@ -754,7 +754,7 @@
         <v>3</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>326.25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -790,7 +790,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>779.2</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -826,7 +826,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>587.2</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11">
@@ -862,7 +862,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>801.6</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="12">
@@ -898,7 +898,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>1663</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="13">
@@ -934,7 +934,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>1037</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14">
@@ -970,7 +970,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>724</v>
+        <v>800</v>
       </c>
     </row>
     <row r="15">
@@ -1006,7 +1006,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>177</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -1042,7 +1042,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>653.8</v>
+        <v>800</v>
       </c>
     </row>
     <row r="17">
@@ -1078,7 +1078,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>1758</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="18">
@@ -1114,7 +1114,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>56.1</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
@@ -1150,7 +1150,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1148</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="20">
@@ -1186,7 +1186,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>905.25</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="21">
@@ -1222,7 +1222,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>918</v>
+        <v>600</v>
       </c>
     </row>
     <row r="22">
@@ -1258,7 +1258,7 @@
         <v>3</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>1806.9</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="23">
@@ -1294,7 +1294,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>672.8</v>
+        <v>700</v>
       </c>
     </row>
     <row r="24">
@@ -1330,7 +1330,7 @@
         <v>2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>619.4</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25">
@@ -1366,7 +1366,7 @@
         <v>2</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>370</v>
+        <v>300</v>
       </c>
     </row>
     <row r="26">
@@ -1402,7 +1402,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>882</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="27">
@@ -1438,7 +1438,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>190.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -1474,7 +1474,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>1696</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="29">
@@ -1510,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>102.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -1546,7 +1546,7 @@
         <v>2</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>258.4</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31">
@@ -1582,7 +1582,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>263</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32">
@@ -1618,7 +1618,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>159</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33">
@@ -1654,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>352</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34">
@@ -1690,7 +1690,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>148</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35">
@@ -1726,7 +1726,7 @@
         <v>2</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>226</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36">
@@ -1762,7 +1762,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>289.85</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37">
@@ -1798,7 +1798,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38">
@@ -1834,7 +1834,7 @@
         <v>4</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>4416</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="39">
@@ -1870,7 +1870,7 @@
         <v>2</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1160</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="40">
@@ -1906,7 +1906,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>889.1</v>
+        <v>700</v>
       </c>
     </row>
     <row r="41">
@@ -1942,7 +1942,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>115.9</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42">
@@ -1978,7 +1978,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>303.05</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43">
@@ -2014,7 +2014,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>710</v>
+        <v>800</v>
       </c>
     </row>
     <row r="44">
@@ -2050,7 +2050,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>1245</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="45">
@@ -2086,7 +2086,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>1009.6</v>
+        <v>800</v>
       </c>
     </row>
     <row r="46">
@@ -2122,7 +2122,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>782</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/day1_excel_foundations/06_sorting_filtering_organizing/d1_m6_sorting_start.xlsx
+++ b/datasets/day1_excel_foundations/06_sorting_filtering_organizing/d1_m6_sorting_start.xlsx
@@ -450,13 +450,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
     <col width="19.5" customWidth="1" min="3" max="3"/>
-    <col width="10.5" customWidth="1" min="4" max="4"/>
+    <col width="14.5" customWidth="1" min="4" max="4"/>
     <col width="22.5" customWidth="1" min="5" max="5"/>
     <col width="12.5" customWidth="1" min="6" max="6"/>
     <col width="10.5" customWidth="1" min="7" max="7"/>
@@ -607,10 +607,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5">
@@ -643,10 +643,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>1400</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="6">
@@ -670,19 +670,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="7">
@@ -692,33 +692,33 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45938</v>
+        <v>45694</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amara Otieno</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -728,33 +728,33 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45458</v>
+        <v>45922</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smart Home</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9">
@@ -800,11 +800,11 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45856</v>
+        <v>46084</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -814,19 +814,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>USB-C Hub 7in1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Accessory</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -836,11 +836,11 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45383</v>
+        <v>45796</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -850,19 +850,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HP Spectre x360</t>
+          <t>Surface Go 4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="12">
@@ -872,33 +872,33 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46317</v>
+        <v>46200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Pixel 9 Pro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>1400</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="13">
@@ -908,33 +908,33 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45857</v>
+        <v>45944</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tendai Moyo</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>Echo Dot 6</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -944,11 +944,11 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45994</v>
+        <v>46365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Tatenda Mpofu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -958,19 +958,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>HP Spectre x360</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>800</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="15">
@@ -980,33 +980,33 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45453</v>
+        <v>45682</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy Tab S10</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smart Home</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16">
@@ -1016,33 +1016,33 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46287</v>
+        <v>46210</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Wireless Mouse Pro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Accessory</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>800</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
@@ -1052,33 +1052,33 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46107</v>
+        <v>45734</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>OnePlus 13</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>1400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18">
@@ -1088,33 +1088,33 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46011</v>
+        <v>46347</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tatenda Mpofu</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bluetooth Headphones</t>
+          <t>Google Nest Hub 3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Accessory</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19">
@@ -1124,11 +1124,11 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45508</v>
+        <v>45902</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1138,19 +1138,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Laptop Sleeve 15in</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Accessory</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>1400</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20">
@@ -1160,11 +1160,11 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45671</v>
+        <v>46065</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1174,16 +1174,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>1400</v>
@@ -1196,11 +1196,11 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45306</v>
+        <v>45824</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rutendo Chikafu</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1210,919 +1210,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>O0021</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45939</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Kudzai Sibanda</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Galaxy Tab S10</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>O0022</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45884</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>iPad Air 6</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>O0023</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45522</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>O0024</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Farai Ncube</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>O0025</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>46363</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Chanda Phiri</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Zambia</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>ThinkPad X1</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>O0026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>46017</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Tendai Moyo</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Echo Dot 6</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>O0027</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>46252</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Simbarashe Mutasa</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>MacBook Air M4</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>O0028</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Chipo Marufu</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Laptop Sleeve 15in</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Accessory</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>O0029</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n">
-        <v>45498</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Kudzai Sibanda</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Bluetooth Headphones</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Accessory</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>O0030</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n">
-        <v>46183</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Simbarashe Mutasa</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Ring Doorbell Pro</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="3" t="n">
         <v>200</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>O0031</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n">
-        <v>45855</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Nyasha Banda</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>USB-C Hub 7in1</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Accessory</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>O0032</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n">
-        <v>45776</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Rutendo Chikafu</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>O0033</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>46040</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Tendai Moyo</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Ring Doorbell Pro</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>O0034</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>45832</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Amara Otieno</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>2</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>O0035</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>46343</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Kagiso Molefe</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Botswana</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Google Nest Hub 3</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>O0036</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>45481</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Kudzai Sibanda</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Wireless Mouse Pro</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Accessory</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>O0037</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>46001</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Simbarashe Mutasa</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Dell XPS 15</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>4</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>O0038</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>45940</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Amara Otieno</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>OnePlus 13</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>O0039</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>45975</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Rutendo Chikafu</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>iPad Air 6</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Tablet</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>O0040</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>46243</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Farai Ncube</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Ring Doorbell Pro</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>O0041</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>45511</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Amara Otieno</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Kenya</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Echo Dot 6</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Smart Home</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>O0042</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>45676</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Tendai Moyo</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Galaxy S24</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>O0043</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>46368</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Tendai Moyo</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Dell XPS 15</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Laptop</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>O0044</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>45538</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Farai Ncube</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Zimbabwe</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Galaxy S24</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="3" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>O0045</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>45494</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Kagiso Molefe</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Botswana</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>iPhone 16</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Smartphone</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/day1_excel_foundations/06_sorting_filtering_organizing/d1_m6_sorting_start.xlsx
+++ b/datasets/day1_excel_foundations/06_sorting_filtering_organizing/d1_m6_sorting_start.xlsx
@@ -1255,7 +1255,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>45 orders, in no particular order. Let's make them answer questions.</t>
+          <t>20 orders, in no particular order. Let's make them answer questions.</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">     (Look at the bottom-left status bar - Excel tells you 'x of 45 records found'.)</t>
+          <t xml:space="preserve">     (Look at the bottom-left status bar - Excel tells you 'x of 20 records found'.)</t>
         </is>
       </c>
     </row>
